--- a/data/processed/DGE_SHAP_Drivers_Forecast_2026.xlsx
+++ b/data/processed/DGE_SHAP_Drivers_Forecast_2026.xlsx
@@ -506,7 +506,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
@@ -551,7 +551,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Macro_Lags_SHAP_USD</t>
+          <t>US_Macro_Lags_SHAP_USD</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-101317.72</v>
+        <v>-95425.22</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-69791.2</v>
+        <v>-103821.45</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-537.47</v>
+        <v>-41339.99</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>2149267.75</v>
+        <v>2085386.75</v>
       </c>
     </row>
     <row r="4">
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>139980.97</v>
+        <v>188682.12</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>-96804.35000000001</v>
+        <v>80623.48</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-5203.45</v>
+        <v>-24588.57</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>2358887.25</v>
+        <v>2570691</v>
       </c>
     </row>
     <row r="5">
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>178106.06</v>
+        <v>274794</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-96682.41</v>
+        <v>32489.95</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>9868.969999999999</v>
+        <v>16246.85</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>2412206.75</v>
+        <v>2649504.25</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-13850.44</v>
+        <v>134423.5</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-290323.41</v>
+        <v>-45853.45</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>17535.16</v>
+        <v>31567.93</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>2034275.75</v>
+        <v>2446111</v>
       </c>
     </row>
     <row r="7">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>66514.03</v>
+        <v>-149847.91</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-163082.27</v>
+        <v>27692.88</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>42086.34</v>
+        <v>67183.87</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>2266433</v>
+        <v>2271000.75</v>
       </c>
     </row>
     <row r="8">
@@ -760,19 +760,19 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-177776.16</v>
+        <v>86561.86</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-181100.53</v>
+        <v>-19574.92</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>59961.22</v>
+        <v>98096.55</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>2021999.38</v>
+        <v>2491056.5</v>
       </c>
     </row>
     <row r="9">
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-326730.81</v>
+        <v>-348183.38</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-177790.19</v>
+        <v>43496.14</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>58335.39</v>
+        <v>71271.5</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1874729.38</v>
+        <v>2092556.25</v>
       </c>
     </row>
     <row r="10">
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-206523.05</v>
+        <v>-235082.84</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>-167452.22</v>
+        <v>32304.25</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>43077.91</v>
+        <v>60314.36</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1990016.88</v>
+        <v>2183507.75</v>
       </c>
     </row>
     <row r="11">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-416209.62</v>
+        <v>-192973.34</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-179603.25</v>
+        <v>50649.66</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>92758.57000000001</v>
+        <v>153954.94</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1817860.12</v>
+        <v>2337603.5</v>
       </c>
     </row>
     <row r="12">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-432210.38</v>
+        <v>-438350.06</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>-186412.28</v>
+        <v>35049.51</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>121529.15</v>
+        <v>196317.33</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1823820.88</v>
+        <v>2118988.75</v>
       </c>
     </row>
     <row r="13">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-432210.38</v>
+        <v>-479243.56</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-186412.28</v>
+        <v>32288.5</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>121529.15</v>
+        <v>192742.62</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1823820.88</v>
+        <v>2071760.88</v>
       </c>
     </row>
     <row r="14">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-325596.81</v>
+        <v>-176615.41</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>-161505.83</v>
+        <v>30015.64</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>-391754.97</v>
+        <v>-387756.06</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>1442057.88</v>
+        <v>1791618.38</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>2320915</v>
+        <v>2325973.75</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>-170652.02</v>
+        <v>-119271.69</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>-163080.02</v>
+        <v>16280.02</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>14098.83</v>
+        <v>36167.61</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>2001281.32</v>
+        <v>2259148.81</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-146066.83</v>
+        <v>-177041.47</v>
       </c>
     </row>
     <row r="4">
@@ -1142,16 +1142,16 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
-        <v>72887.95</v>
+        <v>74459.58</v>
       </c>
     </row>
     <row r="5">
@@ -1175,16 +1175,16 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>52472.52</v>
+        <v>-58688.65</v>
       </c>
     </row>
     <row r="6">
@@ -1208,16 +1208,16 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-40465.41</v>
+        <v>-49746.87</v>
       </c>
     </row>
     <row r="7">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-36786.98</v>
+        <v>49476.06</v>
       </c>
     </row>
     <row r="8">
@@ -1274,16 +1274,16 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>-30646.96</v>
+        <v>-40943.1</v>
       </c>
     </row>
     <row r="9">
@@ -1307,16 +1307,16 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-29797.96</v>
+        <v>-34169.07</v>
       </c>
     </row>
     <row r="10">
@@ -1340,16 +1340,16 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>29730.38</v>
+        <v>-23051.57</v>
       </c>
     </row>
     <row r="11">
@@ -1373,16 +1373,16 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-29369.64</v>
+        <v>23031.79</v>
       </c>
     </row>
     <row r="12">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>25943.2</v>
+        <v>22363.45</v>
       </c>
     </row>
     <row r="13">
@@ -1439,16 +1439,16 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>21773.42</v>
+        <v>20450.45</v>
       </c>
     </row>
     <row r="14">
@@ -1472,16 +1472,16 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>21653.47</v>
+        <v>16986.99</v>
       </c>
     </row>
     <row r="15">
@@ -1505,16 +1505,16 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>20394.43</v>
+        <v>-15604.32</v>
       </c>
     </row>
     <row r="16">
@@ -1538,16 +1538,16 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_5</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>-16075.37</v>
+        <v>-15407.42</v>
       </c>
     </row>
     <row r="17">
@@ -1571,16 +1571,16 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_3</t>
+          <t>us_production_index_diff_lag_4</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-15930.22</v>
+        <v>-13928.49</v>
       </c>
     </row>
     <row r="18">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>68172.16</v>
+        <v>80053.49000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1637,16 +1637,16 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>-59316.06</v>
+        <v>61639.72</v>
       </c>
     </row>
     <row r="20">
@@ -1670,16 +1670,16 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-54278.74</v>
+        <v>54156.35</v>
       </c>
     </row>
     <row r="21">
@@ -1703,16 +1703,16 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G21" s="8" t="n">
-        <v>-52885.11</v>
+        <v>50858.96</v>
       </c>
     </row>
     <row r="22">
@@ -1736,16 +1736,16 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>49109.45</v>
+        <v>-38993.89</v>
       </c>
     </row>
     <row r="23">
@@ -1769,16 +1769,16 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_production_index_diff_lag_4</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>41069.61</v>
+        <v>-33192.19</v>
       </c>
     </row>
     <row r="24">
@@ -1802,16 +1802,16 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-28604.94</v>
+        <v>25478.64</v>
       </c>
     </row>
     <row r="25">
@@ -1835,16 +1835,16 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_4</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
-        <v>-23174.37</v>
+        <v>24122.41</v>
       </c>
     </row>
     <row r="26">
@@ -1868,16 +1868,16 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>22502.35</v>
+        <v>21155.02</v>
       </c>
     </row>
     <row r="27">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G27" s="8" t="n">
-        <v>21685.32</v>
+        <v>20757.06</v>
       </c>
     </row>
     <row r="28">
@@ -1934,16 +1934,16 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-21291.76</v>
+        <v>17802.68</v>
       </c>
     </row>
     <row r="29">
@@ -1967,16 +1967,16 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G29" s="8" t="n">
-        <v>19427.94</v>
+        <v>-16760.9</v>
       </c>
     </row>
     <row r="30">
@@ -2000,16 +2000,16 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>15010.17</v>
+        <v>9723.889999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2033,16 +2033,16 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_production_index_diff_lag_5</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G31" s="8" t="n">
-        <v>12602.13</v>
+        <v>-9200.52</v>
       </c>
     </row>
     <row r="32">
@@ -2066,16 +2066,16 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>us_production_index_diff_lag_6</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-12495.38</v>
+        <v>-8913.950000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2099,16 +2099,16 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-65292.65</v>
+        <v>87383.02</v>
       </c>
     </row>
     <row r="34">
@@ -2132,16 +2132,16 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G34" s="8" t="n">
-        <v>-58655.75</v>
+        <v>57300.3</v>
       </c>
     </row>
     <row r="35">
@@ -2165,16 +2165,16 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-50737.63</v>
+        <v>56783.5</v>
       </c>
     </row>
     <row r="36">
@@ -2198,16 +2198,16 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G36" s="8" t="n">
-        <v>48619.67</v>
+        <v>-51216.98</v>
       </c>
     </row>
     <row r="37">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>45457.24</v>
+        <v>37103.91</v>
       </c>
     </row>
     <row r="38">
@@ -2264,16 +2264,16 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G38" s="8" t="n">
-        <v>33171.98</v>
+        <v>35271.89</v>
       </c>
     </row>
     <row r="39">
@@ -2297,16 +2297,16 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>us_production_index_diff_lag_5</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>33012.77</v>
+        <v>20248.23</v>
       </c>
     </row>
     <row r="40">
@@ -2330,16 +2330,16 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G40" s="8" t="n">
-        <v>24171.61</v>
+        <v>20061.28</v>
       </c>
     </row>
     <row r="41">
@@ -2363,16 +2363,16 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_4</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>23295.54</v>
+        <v>-19242.19</v>
       </c>
     </row>
     <row r="42">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G42" s="8" t="n">
-        <v>22139.11</v>
+        <v>17690.62</v>
       </c>
     </row>
     <row r="43">
@@ -2429,16 +2429,16 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-20705.68</v>
+        <v>16656.97</v>
       </c>
     </row>
     <row r="44">
@@ -2462,16 +2462,16 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G44" s="8" t="n">
-        <v>-18570.43</v>
+        <v>13615.72</v>
       </c>
     </row>
     <row r="45">
@@ -2495,16 +2495,16 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>14058.85</v>
+        <v>-13310.33</v>
       </c>
     </row>
     <row r="46">
@@ -2528,16 +2528,16 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_6</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G46" s="8" t="n">
-        <v>13297.4</v>
+        <v>11140.51</v>
       </c>
     </row>
     <row r="47">
@@ -2561,16 +2561,16 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>13244.61</v>
+        <v>10375.63</v>
       </c>
     </row>
     <row r="48">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-143234.22</v>
+        <v>82375.03999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2627,16 +2627,16 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G49" s="8" t="n">
-        <v>-70517.8</v>
+        <v>-63149.61</v>
       </c>
     </row>
     <row r="50">
@@ -2660,16 +2660,16 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-65678.17999999999</v>
+        <v>55040.58</v>
       </c>
     </row>
     <row r="51">
@@ -2693,16 +2693,16 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G51" s="8" t="n">
-        <v>-49053.72</v>
+        <v>37016.64</v>
       </c>
     </row>
     <row r="52">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>46728</v>
+        <v>27868.86</v>
       </c>
     </row>
     <row r="53">
@@ -2759,16 +2759,16 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G53" s="8" t="n">
-        <v>42661.82</v>
+        <v>-27651.39</v>
       </c>
     </row>
     <row r="54">
@@ -2792,16 +2792,16 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>30528.17</v>
+        <v>-26707.52</v>
       </c>
     </row>
     <row r="55">
@@ -2825,16 +2825,16 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G55" s="8" t="n">
-        <v>-25093.25</v>
+        <v>23874.08</v>
       </c>
     </row>
     <row r="56">
@@ -2858,16 +2858,16 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-25048.13</v>
+        <v>21392.91</v>
       </c>
     </row>
     <row r="57">
@@ -2891,16 +2891,16 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G57" s="8" t="n">
-        <v>20471.13</v>
+        <v>17694.9</v>
       </c>
     </row>
     <row r="58">
@@ -2924,16 +2924,16 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_6</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-18047.1</v>
+        <v>16877.13</v>
       </c>
     </row>
     <row r="59">
@@ -2957,16 +2957,16 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_production_index_diff_lag_5</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G59" s="8" t="n">
-        <v>-16262.32</v>
+        <v>-16255.55</v>
       </c>
     </row>
     <row r="60">
@@ -2990,16 +2990,16 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-13268.66</v>
+        <v>-16006.14</v>
       </c>
     </row>
     <row r="61">
@@ -3023,16 +3023,16 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_4</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G61" s="8" t="n">
-        <v>-13109.75</v>
+        <v>12060.68</v>
       </c>
     </row>
     <row r="62">
@@ -3056,16 +3056,16 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-11922.41</v>
+        <v>-11035.21</v>
       </c>
     </row>
     <row r="63">
@@ -3089,16 +3089,16 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-60624.21</v>
+        <v>-207487.28</v>
       </c>
     </row>
     <row r="64">
@@ -3122,16 +3122,16 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>-59432.88</v>
+        <v>80250.12</v>
       </c>
     </row>
     <row r="65">
@@ -3155,16 +3155,16 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-58593.68</v>
+        <v>-80081.98</v>
       </c>
     </row>
     <row r="66">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>47613.68</v>
+        <v>55551.91</v>
       </c>
     </row>
     <row r="67">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>43488.58</v>
+        <v>49432.76</v>
       </c>
     </row>
     <row r="68">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G68" s="8" t="n">
-        <v>34480.57</v>
+        <v>27184.27</v>
       </c>
     </row>
     <row r="69">
@@ -3287,16 +3287,16 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-27438.15</v>
+        <v>22943.26</v>
       </c>
     </row>
     <row r="70">
@@ -3320,16 +3320,16 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G70" s="8" t="n">
-        <v>24171.12</v>
+        <v>-21052.91</v>
       </c>
     </row>
     <row r="71">
@@ -3353,16 +3353,16 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-21779.6</v>
+        <v>20657.13</v>
       </c>
     </row>
     <row r="72">
@@ -3386,16 +3386,16 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_production_index_diff_lag_5</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G72" s="8" t="n">
-        <v>-20055.73</v>
+        <v>-17148.28</v>
       </c>
     </row>
     <row r="73">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-17018.35</v>
+        <v>16417.24</v>
       </c>
     </row>
     <row r="74">
@@ -3452,16 +3452,16 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G74" s="8" t="n">
-        <v>15764.18</v>
+        <v>-16214.63</v>
       </c>
     </row>
     <row r="75">
@@ -3485,16 +3485,16 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>15479.27</v>
+        <v>13327.58</v>
       </c>
     </row>
     <row r="76">
@@ -3518,16 +3518,16 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_production_index_diff_lag_4</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G76" s="8" t="n">
-        <v>-12684.87</v>
+        <v>-11243.05</v>
       </c>
     </row>
     <row r="77">
@@ -3551,16 +3551,16 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>9844.309999999999</v>
+        <v>9657.690000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3584,16 +3584,16 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-213434.75</v>
+        <v>73131.03999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3617,16 +3617,16 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G79" s="8" t="n">
-        <v>-67177.38</v>
+        <v>56036.27</v>
       </c>
     </row>
     <row r="80">
@@ -3650,16 +3650,16 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-54966.19</v>
+        <v>54059.54</v>
       </c>
     </row>
     <row r="81">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="G81" s="8" t="n">
-        <v>51790.12</v>
+        <v>-43824.09</v>
       </c>
     </row>
     <row r="82">
@@ -3716,16 +3716,16 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>51062.84</v>
+        <v>-42690.74</v>
       </c>
     </row>
     <row r="83">
@@ -3749,16 +3749,16 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G83" s="8" t="n">
-        <v>-47755.98</v>
+        <v>31807.21</v>
       </c>
     </row>
     <row r="84">
@@ -3782,16 +3782,16 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-25440.5</v>
+        <v>-29999.96</v>
       </c>
     </row>
     <row r="85">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="G85" s="8" t="n">
-        <v>-20804.62</v>
+        <v>18461.24</v>
       </c>
     </row>
     <row r="86">
@@ -3853,11 +3853,11 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>20592.27</v>
+        <v>16944.31</v>
       </c>
     </row>
     <row r="87">
@@ -3881,16 +3881,16 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G87" s="8" t="n">
-        <v>-15183.82</v>
+        <v>15234.48</v>
       </c>
     </row>
     <row r="88">
@@ -3914,16 +3914,16 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_production_index_diff_lag_6</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-12402.96</v>
+        <v>13227.83</v>
       </c>
     </row>
     <row r="89">
@@ -3947,16 +3947,16 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G89" s="8" t="n">
-        <v>12399.96</v>
+        <v>13006.46</v>
       </c>
     </row>
     <row r="90">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>12259.85</v>
+        <v>-10227.92</v>
       </c>
     </row>
     <row r="91">
@@ -4013,16 +4013,16 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G91" s="8" t="n">
-        <v>9990.49</v>
+        <v>-9977.82</v>
       </c>
     </row>
     <row r="92">
@@ -4046,16 +4046,16 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-9898.02</v>
+        <v>9186.92</v>
       </c>
     </row>
     <row r="93">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-219337.33</v>
+        <v>-300145.09</v>
       </c>
     </row>
     <row r="94">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="G94" s="8" t="n">
-        <v>-136220.03</v>
+        <v>-185699.47</v>
       </c>
     </row>
     <row r="95">
@@ -4145,16 +4145,16 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-67641.22</v>
+        <v>64964.88</v>
       </c>
     </row>
     <row r="96">
@@ -4178,16 +4178,16 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G96" s="8" t="n">
-        <v>-59541.64</v>
+        <v>60873.16</v>
       </c>
     </row>
     <row r="97">
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>51189.15</v>
+        <v>38879.48</v>
       </c>
     </row>
     <row r="98">
@@ -4244,16 +4244,16 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G98" s="8" t="n">
-        <v>43210.62</v>
+        <v>36385.08</v>
       </c>
     </row>
     <row r="99">
@@ -4277,16 +4277,16 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-42434.99</v>
+        <v>21280.17</v>
       </c>
     </row>
     <row r="100">
@@ -4310,16 +4310,16 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G100" s="8" t="n">
-        <v>-25258.42</v>
+        <v>15237.47</v>
       </c>
     </row>
     <row r="101">
@@ -4343,16 +4343,16 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-17730.97</v>
+        <v>15089.11</v>
       </c>
     </row>
     <row r="102">
@@ -4376,16 +4376,16 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G102" s="8" t="n">
-        <v>-17621.33</v>
+        <v>-14863.39</v>
       </c>
     </row>
     <row r="103">
@@ -4409,16 +4409,16 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>17568.48</v>
+        <v>13404.81</v>
       </c>
     </row>
     <row r="104">
@@ -4442,16 +4442,16 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G104" s="8" t="n">
-        <v>16714.58</v>
+        <v>11474.78</v>
       </c>
     </row>
     <row r="105">
@@ -4475,16 +4475,16 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_4</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>-12958.41</v>
+        <v>8478.09</v>
       </c>
     </row>
     <row r="106">
@@ -4508,16 +4508,16 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G106" s="8" t="n">
-        <v>-12857.71</v>
+        <v>-7691.48</v>
       </c>
     </row>
     <row r="107">
@@ -4541,16 +4541,16 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>12483.27</v>
+        <v>-7334.05</v>
       </c>
     </row>
     <row r="108">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-229950.39</v>
+        <v>-319959.94</v>
       </c>
     </row>
     <row r="109">
@@ -4607,16 +4607,16 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G109" s="8" t="n">
-        <v>-61394.54</v>
+        <v>67031.19</v>
       </c>
     </row>
     <row r="110">
@@ -4640,16 +4640,16 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>-55034.23</v>
+        <v>38801.09</v>
       </c>
     </row>
     <row r="111">
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="G111" s="8" t="n">
-        <v>52686.65</v>
+        <v>36981.05</v>
       </c>
     </row>
     <row r="112">
@@ -4706,16 +4706,16 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>-43730.89</v>
+        <v>-31496.04</v>
       </c>
     </row>
     <row r="113">
@@ -4739,16 +4739,16 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G113" s="8" t="n">
-        <v>35835.55</v>
+        <v>-28201.77</v>
       </c>
     </row>
     <row r="114">
@@ -4772,16 +4772,16 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>-25234.54</v>
+        <v>26743.62</v>
       </c>
     </row>
     <row r="115">
@@ -4805,16 +4805,16 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>-22815.87</v>
+        <v>16651.25</v>
       </c>
     </row>
     <row r="116">
@@ -4838,16 +4838,16 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>17501.8</v>
+        <v>16355.57</v>
       </c>
     </row>
     <row r="117">
@@ -4871,16 +4871,16 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>-17426.19</v>
+        <v>15912.86</v>
       </c>
     </row>
     <row r="118">
@@ -4904,16 +4904,16 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>-13355.44</v>
+        <v>13423.28</v>
       </c>
     </row>
     <row r="119">
@@ -4937,16 +4937,16 @@
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>12098.03</v>
+        <v>9972.16</v>
       </c>
     </row>
     <row r="120">
@@ -4970,16 +4970,16 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>-11525.95</v>
+        <v>-9385.059999999999</v>
       </c>
     </row>
     <row r="121">
@@ -5003,16 +5003,16 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G121" s="8" t="n">
-        <v>-11425.55</v>
+        <v>7999.81</v>
       </c>
     </row>
     <row r="122">
@@ -5036,16 +5036,16 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_4</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>9825.700000000001</v>
+        <v>6092.88</v>
       </c>
     </row>
     <row r="123">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>-222783.39</v>
+        <v>-317696.53</v>
       </c>
     </row>
     <row r="124">
@@ -5102,16 +5102,16 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>month</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G124" s="8" t="n">
-        <v>-217028.95</v>
+        <v>115203.76</v>
       </c>
     </row>
     <row r="125">
@@ -5135,16 +5135,16 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>85235.48</v>
+        <v>80351.49000000001</v>
       </c>
     </row>
     <row r="126">
@@ -5168,16 +5168,16 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G126" s="8" t="n">
-        <v>-66362.22</v>
+        <v>68219.14</v>
       </c>
     </row>
     <row r="127">
@@ -5201,16 +5201,16 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>-58905.07</v>
+        <v>43914.9</v>
       </c>
     </row>
     <row r="128">
@@ -5234,16 +5234,16 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G128" s="8" t="n">
-        <v>47658.96</v>
+        <v>-22289.95</v>
       </c>
     </row>
     <row r="129">
@@ -5267,16 +5267,16 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>-42432.42</v>
+        <v>19080.68</v>
       </c>
     </row>
     <row r="130">
@@ -5300,16 +5300,16 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>-26514.55</v>
+        <v>-15781.14</v>
       </c>
     </row>
     <row r="131">
@@ -5333,16 +5333,16 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>-21128.54</v>
+        <v>14418.71</v>
       </c>
     </row>
     <row r="132">
@@ -5366,16 +5366,16 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G132" s="8" t="n">
-        <v>-20276.83</v>
+        <v>13741.03</v>
       </c>
     </row>
     <row r="133">
@@ -5399,16 +5399,16 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>-19315.17</v>
+        <v>10778.4</v>
       </c>
     </row>
     <row r="134">
@@ -5432,16 +5432,16 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G134" s="8" t="n">
-        <v>17966.8</v>
+        <v>-10279.42</v>
       </c>
     </row>
     <row r="135">
@@ -5465,16 +5465,16 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>-16931.79</v>
+        <v>8390.610000000001</v>
       </c>
     </row>
     <row r="136">
@@ -5498,16 +5498,16 @@
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G136" s="8" t="n">
-        <v>16517.33</v>
+        <v>-8226.860000000001</v>
       </c>
     </row>
     <row r="137">
@@ -5531,16 +5531,16 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>12392.43</v>
+        <v>-4792.78</v>
       </c>
     </row>
     <row r="138">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>-230953.58</v>
+        <v>-282463.31</v>
       </c>
     </row>
     <row r="139">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="G139" s="8" t="n">
-        <v>-215688.25</v>
+        <v>-215078.41</v>
       </c>
     </row>
     <row r="140">
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>111126.88</v>
+        <v>141181.2</v>
       </c>
     </row>
     <row r="141">
@@ -5663,16 +5663,16 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G141" s="8" t="n">
-        <v>-67901.89999999999</v>
+        <v>63676.09</v>
       </c>
     </row>
     <row r="142">
@@ -5696,16 +5696,16 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>-58901.8</v>
+        <v>42189.86</v>
       </c>
     </row>
     <row r="143">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="G143" s="8" t="n">
-        <v>47613.68</v>
+        <v>-27237.81</v>
       </c>
     </row>
     <row r="144">
@@ -5762,16 +5762,16 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>-40776.63</v>
+        <v>17289.01</v>
       </c>
     </row>
     <row r="145">
@@ -5795,16 +5795,16 @@
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G145" s="8" t="n">
-        <v>-27335.47</v>
+        <v>-16987.55</v>
       </c>
     </row>
     <row r="146">
@@ -5828,16 +5828,16 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>-26706.62</v>
+        <v>15900.12</v>
       </c>
     </row>
     <row r="147">
@@ -5861,16 +5861,16 @@
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G147" s="8" t="n">
-        <v>-23350.54</v>
+        <v>15259.61</v>
       </c>
     </row>
     <row r="148">
@@ -5894,16 +5894,16 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>-22399.71</v>
+        <v>12467.37</v>
       </c>
     </row>
     <row r="149">
@@ -5927,16 +5927,16 @@
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G149" s="8" t="n">
-        <v>-20783.01</v>
+        <v>11970.57</v>
       </c>
     </row>
     <row r="150">
@@ -5960,16 +5960,16 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>18160.7</v>
+        <v>10470.91</v>
       </c>
     </row>
     <row r="151">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="G151" s="8" t="n">
-        <v>16546.42</v>
+        <v>8889.049999999999</v>
       </c>
     </row>
     <row r="152">
@@ -6026,16 +6026,16 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>12025.6</v>
+        <v>-7475.68</v>
       </c>
     </row>
     <row r="153">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>-230953.58</v>
+        <v>-285346.91</v>
       </c>
     </row>
     <row r="154">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="G154" s="8" t="n">
-        <v>-215688.25</v>
+        <v>-209435.81</v>
       </c>
     </row>
     <row r="155">
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>111126.88</v>
+        <v>137515.64</v>
       </c>
     </row>
     <row r="156">
@@ -6158,16 +6158,16 @@
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G156" s="8" t="n">
-        <v>-67901.89999999999</v>
+        <v>52637.13</v>
       </c>
     </row>
     <row r="157">
@@ -6191,16 +6191,16 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>-58901.8</v>
+        <v>42189.86</v>
       </c>
     </row>
     <row r="158">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="G158" s="8" t="n">
-        <v>47613.68</v>
+        <v>-34107.7</v>
       </c>
     </row>
     <row r="159">
@@ -6257,16 +6257,16 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>-40776.63</v>
+        <v>-16971.42</v>
       </c>
     </row>
     <row r="160">
@@ -6290,16 +6290,16 @@
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G160" s="8" t="n">
-        <v>-27335.47</v>
+        <v>16789.1</v>
       </c>
     </row>
     <row r="161">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>-26706.62</v>
+        <v>-15926.92</v>
       </c>
     </row>
     <row r="162">
@@ -6356,16 +6356,16 @@
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G162" s="8" t="n">
-        <v>-23350.54</v>
+        <v>15536.8</v>
       </c>
     </row>
     <row r="163">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>-22399.71</v>
+        <v>15376.42</v>
       </c>
     </row>
     <row r="164">
@@ -6422,16 +6422,16 @@
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G164" s="8" t="n">
-        <v>-20783.01</v>
+        <v>12558.24</v>
       </c>
     </row>
     <row r="165">
@@ -6455,16 +6455,16 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>18160.7</v>
+        <v>11777.09</v>
       </c>
     </row>
     <row r="166">
@@ -6488,16 +6488,16 @@
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G166" s="8" t="n">
-        <v>16546.42</v>
+        <v>10794.88</v>
       </c>
     </row>
     <row r="167">
@@ -6521,16 +6521,16 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>12025.6</v>
+        <v>-7556.96</v>
       </c>
     </row>
     <row r="168">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>-401749.62</v>
+        <v>-441653.41</v>
       </c>
     </row>
     <row r="169">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>revenue_rolling_6m_std</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="G169" s="8" t="n">
-        <v>-227185.58</v>
+        <v>-174841.19</v>
       </c>
     </row>
     <row r="170">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_std</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>-124498.03</v>
+        <v>74021.60000000001</v>
       </c>
     </row>
     <row r="171">
@@ -6653,16 +6653,16 @@
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>year</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G171" s="8" t="n">
-        <v>-64163.84</v>
+        <v>40157.45</v>
       </c>
     </row>
     <row r="172">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>47013.46</v>
+        <v>-27754.04</v>
       </c>
     </row>
     <row r="173">
@@ -6719,16 +6719,16 @@
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="G173" s="8" t="n">
-        <v>-45532.47</v>
+        <v>-24971.59</v>
       </c>
     </row>
     <row r="174">
@@ -6752,16 +6752,16 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>-35755.84</v>
+        <v>-20780.08</v>
       </c>
     </row>
     <row r="175">
@@ -6785,16 +6785,16 @@
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G175" s="8" t="n">
-        <v>-24692.34</v>
+        <v>18655.19</v>
       </c>
     </row>
     <row r="176">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>-21984.79</v>
+        <v>-17323.73</v>
       </c>
     </row>
     <row r="177">
@@ -6856,11 +6856,11 @@
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G177" s="8" t="n">
-        <v>18021.4</v>
+        <v>13190.49</v>
       </c>
     </row>
     <row r="178">
@@ -6884,16 +6884,16 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>-17700.03</v>
+        <v>12627.11</v>
       </c>
     </row>
     <row r="179">
@@ -6917,16 +6917,16 @@
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G179" s="8" t="n">
-        <v>-16883.48</v>
+        <v>11851.15</v>
       </c>
     </row>
     <row r="180">
@@ -6950,16 +6950,16 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>15704.05</v>
+        <v>10395.79</v>
       </c>
     </row>
     <row r="181">
@@ -6983,16 +6983,16 @@
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G181" s="8" t="n">
-        <v>-14036.38</v>
+        <v>-7503.94</v>
       </c>
     </row>
     <row r="182">
@@ -7016,16 +7016,16 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_production_index_diff_lag_4</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>10148.38</v>
+        <v>4382.6</v>
       </c>
     </row>
   </sheetData>
@@ -7042,7 +7042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>139675.27</v>
+        <v>166851.95</v>
       </c>
     </row>
     <row r="4">
@@ -7104,16 +7104,16 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_3m_std</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>107842.81</v>
+        <v>95967.57000000001</v>
       </c>
     </row>
     <row r="5">
@@ -7122,16 +7122,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>revenue_rolling_3m_std</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>76266.07000000001</v>
+        <v>80694.50999999999</v>
       </c>
     </row>
     <row r="6">
@@ -7140,16 +7140,16 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_1</t>
+          <t>revenue_lag_2</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>60303.64</v>
+        <v>71982.5</v>
       </c>
     </row>
     <row r="7">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_2</t>
+          <t>revenue_rolling_6m_mean</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>57291.67</v>
+        <v>61239.8</v>
       </c>
     </row>
     <row r="8">
@@ -7176,16 +7176,16 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_2</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>55174.19</v>
+        <v>33236.86</v>
       </c>
     </row>
     <row r="9">
@@ -7194,16 +7194,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_3</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>51455.2</v>
+        <v>28303.9</v>
       </c>
     </row>
     <row r="10">
@@ -7212,16 +7212,16 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>revenue_rolling_6m_mean</t>
+          <t>us_durable_goods_orders_musd_diff_lag_6</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>24914.37</v>
+        <v>21105.85</v>
       </c>
     </row>
     <row r="11">
@@ -7230,16 +7230,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_6</t>
+          <t>revenue_lag_1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>21775.32</v>
+        <v>20203.89</v>
       </c>
     </row>
     <row r="12">
@@ -7248,16 +7248,16 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_3</t>
+          <t>us_production_index_diff_lag_2</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>21164.74</v>
+        <v>16795.71</v>
       </c>
     </row>
     <row r="13">
@@ -7266,16 +7266,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_2</t>
+          <t>revenue_lag_3</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>17266.94</v>
+        <v>13448.9</v>
       </c>
     </row>
     <row r="14">
@@ -7284,16 +7284,16 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_4</t>
+          <t>us_durable_goods_orders_musd_diff_lag_5</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>15849.92</v>
+        <v>11355.91</v>
       </c>
     </row>
     <row r="15">
@@ -7302,16 +7302,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>revenue_lag_3</t>
+          <t>us_production_index_diff_lag_3</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>15605.82</v>
+        <v>10641.25</v>
       </c>
     </row>
     <row r="16">
@@ -7320,16 +7320,16 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>revenue_lag_1</t>
+          <t>us_durable_goods_orders_musd_diff_lag_1</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Revenue Lags / Rolling</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>15342.88</v>
+        <v>10462.28</v>
       </c>
     </row>
     <row r="17">
@@ -7338,16 +7338,16 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>de_orders_index_lag_5</t>
+          <t>us_durable_goods_orders_musd_diff_lag_2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>15010.39</v>
+        <v>9243.93</v>
       </c>
     </row>
     <row r="18">
@@ -7356,16 +7356,16 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_6</t>
+          <t>us_durable_goods_orders_musd_diff_lag_4</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>12755.09</v>
+        <v>7994.64</v>
       </c>
     </row>
     <row r="19">
@@ -7374,16 +7374,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_3</t>
+          <t>us_production_index_diff_lag_4</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>11645.52</v>
+        <v>7421.17</v>
       </c>
     </row>
     <row r="20">
@@ -7392,16 +7392,16 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>us_production_index_diff_lag_5</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>8323.389999999999</v>
+        <v>7380.04</v>
       </c>
     </row>
     <row r="21">
@@ -7410,16 +7410,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_1</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7890.64</v>
+        <v>7139.77</v>
       </c>
     </row>
     <row r="22">
@@ -7428,16 +7428,16 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>de_production_index_diff_lag_1</t>
+          <t>us_production_index_diff_lag_6</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>7767.18</v>
+        <v>5239.99</v>
       </c>
     </row>
     <row r="23">
@@ -7446,16 +7446,16 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_4</t>
+          <t>us_production_index_diff_lag_1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>US Macro Lags</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7082.62</v>
+        <v>2832.74</v>
       </c>
     </row>
     <row r="24">
@@ -7464,16 +7464,16 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>us_durable_goods_orders_musd_diff_lag_5</t>
+          <t>revenue_rolling_3m_mean</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Revenue Lags / Rolling</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>6868.13</v>
+        <v>1683.43</v>
       </c>
     </row>
     <row r="25">
@@ -7482,232 +7482,16 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>us_production_index_diff_lag_5</t>
+          <t>is_q4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Macro Lags</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>6779.94</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>de_orders_index_lag_3</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>6152.11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>us_production_index_diff_lag_6</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>5438.29</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>de_production_index_diff_lag_6</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>4306.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>us_production_index_diff_lag_4</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>4205.79</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>de_production_index_diff_lag_5</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>3186.33</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>us_durable_goods_orders_musd_diff_lag_2</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>2886.41</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>us_production_index_diff_lag_1</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>2486.31</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>us_production_index_diff_lag_3</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>2097.65</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>de_production_index_diff_lag_2</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Macro Lags</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>1274.07</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>quarter</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1085.54</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>revenue_rolling_3m_mean</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Revenue Lags / Rolling</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>731.92</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>is_q4</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>50.21</v>
+        <v>409.9</v>
       </c>
     </row>
   </sheetData>
@@ -7724,7 +7508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7746,123 +7530,107 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Base_Value_USD</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Month in YYYYMM format</t>
+          <t>XGBoost model intercept E[f(x)] – average prediction over training data</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Base_Value_USD</t>
+          <t>Revenue_Lags_Rolling_SHAP_USD</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>XGBoost model intercept: E[f(x)] = 2,320,915 USD (average prediction over training data)</t>
+          <t>Sum of SHAP for revenue_lag_1/2/3 and rolling mean/std features</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Revenue_Lags_Rolling_SHAP_USD</t>
+          <t>US_Macro_Lags_SHAP_USD</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Sum of SHAP values for revenue_lag_1/2/3 and rolling mean/std features</t>
+          <t>Sum of SHAP for US DGORDER diff lags + US INDPRO diff lags (1-6)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Macro_Lags_SHAP_USD</t>
+          <t>Calendar_SHAP_USD</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Sum of SHAP values for all macro lag features (DE orders, DE/US production, US DGORDER)</t>
+          <t>Sum of SHAP for month, quarter, year, is_q4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Calendar_SHAP_USD</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Sum of SHAP values for month, quarter, year, is_q4</t>
-        </is>
+          <t>Forecast_USD</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f> Base_Value + Revenue_SHAP + Macro_SHAP + Calendar_SHAP</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Forecast_USD</t>
-        </is>
-      </c>
-      <c r="B7" s="4">
-        <f> Base_Value + Revenue_SHAP + Macro_SHAP + Calendar_SHAP (sum decomposition)</f>
-        <v/>
+          <t>SHAP_Value_USD</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Signed feature contribution relative to base value (positive = pushes up)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>SHAP_Value_USD</t>
+          <t>Mean_Abs_SHAP_USD</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Signed contribution of one feature to one prediction relative to base value (USD)</t>
+          <t>Average |SHAP| across 12 forecast months – global feature importance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mean_Abs_SHAP_USD</t>
+          <t>DE macro</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Average absolute SHAP value across all 12 forecast months – global feature importance</t>
+          <t>Excluded from model – no causal link between DE domestic orders and US revenue</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Positive SHAP = feature pushes prediction above base value; negative = below</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Limitation</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Synthetic data – absolute values demonstrate methodology only</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic data – values demonstrate methodology only</t>
         </is>
       </c>
     </row>
